--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z967"/>
+  <dimension ref="A1:Z969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55299,14 +55299,14 @@
     <row r="942" ht="15" customHeight="1">
       <c r="A942" t="inlineStr">
         <is>
-          <t>A 1927-2024</t>
+          <t>A 2044-2024</t>
         </is>
       </c>
       <c r="B942" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55319,7 +55319,7 @@
         </is>
       </c>
       <c r="G942" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -55356,14 +55356,14 @@
     <row r="943" ht="15" customHeight="1">
       <c r="A943" t="inlineStr">
         <is>
-          <t>A 2044-2024</t>
+          <t>A 2042-2024</t>
         </is>
       </c>
       <c r="B943" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55376,7 +55376,7 @@
         </is>
       </c>
       <c r="G943" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -55413,14 +55413,14 @@
     <row r="944" ht="15" customHeight="1">
       <c r="A944" t="inlineStr">
         <is>
-          <t>A 2042-2024</t>
+          <t>A 1927-2024</t>
         </is>
       </c>
       <c r="B944" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         </is>
       </c>
       <c r="G944" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55641,14 +55641,14 @@
     <row r="948" ht="15" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>A 2947-2024</t>
+          <t>A 2965-2024</t>
         </is>
       </c>
       <c r="B948" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -55698,14 +55698,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 2964-2024</t>
+          <t>A 2947-2024</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55755,14 +55755,14 @@
     <row r="950" ht="15" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>A 2965-2024</t>
+          <t>A 2964-2024</t>
         </is>
       </c>
       <c r="B950" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55812,14 +55812,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 3506-2024</t>
+          <t>A 3510-2024</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55869,14 +55869,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 3510-2024</t>
+          <t>A 3506-2024</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56211,14 +56211,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 4766-2024</t>
+          <t>A 4767-2024</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56275,7 +56275,7 @@
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56325,14 +56325,14 @@
     <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 4767-2024</t>
+          <t>A 4766-2024</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -56382,14 +56382,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 4871-2024</t>
+          <t>A 5045-2024</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56439,14 +56439,14 @@
     <row r="962" ht="15" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>A 5045-2024</t>
+          <t>A 4871-2024</t>
         </is>
       </c>
       <c r="B962" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56615,14 +56615,14 @@
     <row r="965" ht="15" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>A 6009-2024</t>
+          <t>A 5982-2024</t>
         </is>
       </c>
       <c r="B965" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         </is>
       </c>
       <c r="G965" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -56672,14 +56672,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 5982-2024</t>
+          <t>A 6020-2024</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56726,62 +56726,176 @@
       </c>
       <c r="R966" s="2" t="inlineStr"/>
     </row>
-    <row r="967">
+    <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 6020-2024</t>
+          <t>A 6009-2024</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G967" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H967" t="n">
+        <v>0</v>
+      </c>
+      <c r="I967" t="n">
+        <v>0</v>
+      </c>
+      <c r="J967" t="n">
+        <v>0</v>
+      </c>
+      <c r="K967" t="n">
+        <v>0</v>
+      </c>
+      <c r="L967" t="n">
+        <v>0</v>
+      </c>
+      <c r="M967" t="n">
+        <v>0</v>
+      </c>
+      <c r="N967" t="n">
+        <v>0</v>
+      </c>
+      <c r="O967" t="n">
+        <v>0</v>
+      </c>
+      <c r="P967" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q967" t="n">
+        <v>0</v>
+      </c>
+      <c r="R967" s="2" t="inlineStr"/>
+    </row>
+    <row r="968" ht="15" customHeight="1">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>A 6100-2024</t>
+        </is>
+      </c>
+      <c r="B968" s="1" t="n">
         <v>45337</v>
       </c>
-      <c r="D967" t="inlineStr">
-        <is>
-          <t>KRONOBERGS LÄN</t>
-        </is>
-      </c>
-      <c r="E967" t="inlineStr">
-        <is>
-          <t>ALVESTA</t>
-        </is>
-      </c>
-      <c r="G967" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H967" t="n">
-        <v>0</v>
-      </c>
-      <c r="I967" t="n">
-        <v>0</v>
-      </c>
-      <c r="J967" t="n">
-        <v>0</v>
-      </c>
-      <c r="K967" t="n">
-        <v>0</v>
-      </c>
-      <c r="L967" t="n">
-        <v>0</v>
-      </c>
-      <c r="M967" t="n">
-        <v>0</v>
-      </c>
-      <c r="N967" t="n">
-        <v>0</v>
-      </c>
-      <c r="O967" t="n">
-        <v>0</v>
-      </c>
-      <c r="P967" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q967" t="n">
-        <v>0</v>
-      </c>
-      <c r="R967" s="2" t="inlineStr"/>
+      <c r="C968" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G968" t="n">
+        <v>2</v>
+      </c>
+      <c r="H968" t="n">
+        <v>0</v>
+      </c>
+      <c r="I968" t="n">
+        <v>0</v>
+      </c>
+      <c r="J968" t="n">
+        <v>0</v>
+      </c>
+      <c r="K968" t="n">
+        <v>0</v>
+      </c>
+      <c r="L968" t="n">
+        <v>0</v>
+      </c>
+      <c r="M968" t="n">
+        <v>0</v>
+      </c>
+      <c r="N968" t="n">
+        <v>0</v>
+      </c>
+      <c r="O968" t="n">
+        <v>0</v>
+      </c>
+      <c r="P968" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q968" t="n">
+        <v>0</v>
+      </c>
+      <c r="R968" s="2" t="inlineStr"/>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>A 6094-2024</t>
+        </is>
+      </c>
+      <c r="B969" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C969" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G969" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H969" t="n">
+        <v>0</v>
+      </c>
+      <c r="I969" t="n">
+        <v>0</v>
+      </c>
+      <c r="J969" t="n">
+        <v>0</v>
+      </c>
+      <c r="K969" t="n">
+        <v>0</v>
+      </c>
+      <c r="L969" t="n">
+        <v>0</v>
+      </c>
+      <c r="M969" t="n">
+        <v>0</v>
+      </c>
+      <c r="N969" t="n">
+        <v>0</v>
+      </c>
+      <c r="O969" t="n">
+        <v>0</v>
+      </c>
+      <c r="P969" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q969" t="n">
+        <v>0</v>
+      </c>
+      <c r="R969" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z969"/>
+  <dimension ref="A1:Z975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55527,14 +55527,14 @@
     <row r="946" ht="15" customHeight="1">
       <c r="A946" t="inlineStr">
         <is>
-          <t>A 2528-2024</t>
+          <t>A 2557-2024</t>
         </is>
       </c>
       <c r="B946" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -55584,14 +55584,14 @@
     <row r="947" ht="15" customHeight="1">
       <c r="A947" t="inlineStr">
         <is>
-          <t>A 2557-2024</t>
+          <t>A 2528-2024</t>
         </is>
       </c>
       <c r="B947" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -55648,7 +55648,7 @@
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55812,14 +55812,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 3510-2024</t>
+          <t>A 3506-2024</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55869,14 +55869,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 3506-2024</t>
+          <t>A 3510-2024</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56040,14 +56040,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 4733-2024</t>
+          <t>A 4722-2024</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -56097,14 +56097,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 4722-2024</t>
+          <t>A 4738-2024</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -56154,14 +56154,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 4738-2024</t>
+          <t>A 4733-2024</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -56211,14 +56211,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 4767-2024</t>
+          <t>A 4766-2024</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56268,14 +56268,14 @@
     <row r="959" ht="15" customHeight="1">
       <c r="A959" t="inlineStr">
         <is>
-          <t>A 4756-2024</t>
+          <t>A 4767-2024</t>
         </is>
       </c>
       <c r="B959" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="H959" t="n">
         <v>0</v>
@@ -56325,14 +56325,14 @@
     <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 4766-2024</t>
+          <t>A 4756-2024</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -56382,14 +56382,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 5045-2024</t>
+          <t>A 4871-2024</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56439,14 +56439,14 @@
     <row r="962" ht="15" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>A 4871-2024</t>
+          <t>A 5045-2024</t>
         </is>
       </c>
       <c r="B962" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45336</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56672,14 +56672,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 6020-2024</t>
+          <t>A 6009-2024</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56729,14 +56729,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 6009-2024</t>
+          <t>A 6020-2024</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56793,7 +56793,7 @@
         <v>45337</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
       </c>
       <c r="R968" s="2" t="inlineStr"/>
     </row>
-    <row r="969">
+    <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
           <t>A 6094-2024</t>
@@ -56850,7 +56850,7 @@
         <v>45337</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56896,6 +56896,348 @@
         <v>0</v>
       </c>
       <c r="R969" s="2" t="inlineStr"/>
+    </row>
+    <row r="970" ht="15" customHeight="1">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>A 6365-2024</t>
+        </is>
+      </c>
+      <c r="B970" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C970" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G970" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H970" t="n">
+        <v>0</v>
+      </c>
+      <c r="I970" t="n">
+        <v>0</v>
+      </c>
+      <c r="J970" t="n">
+        <v>0</v>
+      </c>
+      <c r="K970" t="n">
+        <v>0</v>
+      </c>
+      <c r="L970" t="n">
+        <v>0</v>
+      </c>
+      <c r="M970" t="n">
+        <v>0</v>
+      </c>
+      <c r="N970" t="n">
+        <v>0</v>
+      </c>
+      <c r="O970" t="n">
+        <v>0</v>
+      </c>
+      <c r="P970" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q970" t="n">
+        <v>0</v>
+      </c>
+      <c r="R970" s="2" t="inlineStr"/>
+    </row>
+    <row r="971" ht="15" customHeight="1">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>A 6386-2024</t>
+        </is>
+      </c>
+      <c r="B971" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C971" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G971" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H971" t="n">
+        <v>0</v>
+      </c>
+      <c r="I971" t="n">
+        <v>0</v>
+      </c>
+      <c r="J971" t="n">
+        <v>0</v>
+      </c>
+      <c r="K971" t="n">
+        <v>0</v>
+      </c>
+      <c r="L971" t="n">
+        <v>0</v>
+      </c>
+      <c r="M971" t="n">
+        <v>0</v>
+      </c>
+      <c r="N971" t="n">
+        <v>0</v>
+      </c>
+      <c r="O971" t="n">
+        <v>0</v>
+      </c>
+      <c r="P971" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q971" t="n">
+        <v>0</v>
+      </c>
+      <c r="R971" s="2" t="inlineStr"/>
+    </row>
+    <row r="972" ht="15" customHeight="1">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>A 6367-2024</t>
+        </is>
+      </c>
+      <c r="B972" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C972" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G972" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H972" t="n">
+        <v>0</v>
+      </c>
+      <c r="I972" t="n">
+        <v>0</v>
+      </c>
+      <c r="J972" t="n">
+        <v>0</v>
+      </c>
+      <c r="K972" t="n">
+        <v>0</v>
+      </c>
+      <c r="L972" t="n">
+        <v>0</v>
+      </c>
+      <c r="M972" t="n">
+        <v>0</v>
+      </c>
+      <c r="N972" t="n">
+        <v>0</v>
+      </c>
+      <c r="O972" t="n">
+        <v>0</v>
+      </c>
+      <c r="P972" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q972" t="n">
+        <v>0</v>
+      </c>
+      <c r="R972" s="2" t="inlineStr"/>
+    </row>
+    <row r="973" ht="15" customHeight="1">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>A 6368-2024</t>
+        </is>
+      </c>
+      <c r="B973" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C973" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G973" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H973" t="n">
+        <v>0</v>
+      </c>
+      <c r="I973" t="n">
+        <v>0</v>
+      </c>
+      <c r="J973" t="n">
+        <v>0</v>
+      </c>
+      <c r="K973" t="n">
+        <v>0</v>
+      </c>
+      <c r="L973" t="n">
+        <v>0</v>
+      </c>
+      <c r="M973" t="n">
+        <v>0</v>
+      </c>
+      <c r="N973" t="n">
+        <v>0</v>
+      </c>
+      <c r="O973" t="n">
+        <v>0</v>
+      </c>
+      <c r="P973" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q973" t="n">
+        <v>0</v>
+      </c>
+      <c r="R973" s="2" t="inlineStr"/>
+    </row>
+    <row r="974" ht="15" customHeight="1">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>A 6360-2024</t>
+        </is>
+      </c>
+      <c r="B974" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C974" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G974" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H974" t="n">
+        <v>0</v>
+      </c>
+      <c r="I974" t="n">
+        <v>0</v>
+      </c>
+      <c r="J974" t="n">
+        <v>0</v>
+      </c>
+      <c r="K974" t="n">
+        <v>0</v>
+      </c>
+      <c r="L974" t="n">
+        <v>0</v>
+      </c>
+      <c r="M974" t="n">
+        <v>0</v>
+      </c>
+      <c r="N974" t="n">
+        <v>0</v>
+      </c>
+      <c r="O974" t="n">
+        <v>0</v>
+      </c>
+      <c r="P974" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q974" t="n">
+        <v>0</v>
+      </c>
+      <c r="R974" s="2" t="inlineStr"/>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>A 6370-2024</t>
+        </is>
+      </c>
+      <c r="B975" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C975" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G975" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H975" t="n">
+        <v>0</v>
+      </c>
+      <c r="I975" t="n">
+        <v>0</v>
+      </c>
+      <c r="J975" t="n">
+        <v>0</v>
+      </c>
+      <c r="K975" t="n">
+        <v>0</v>
+      </c>
+      <c r="L975" t="n">
+        <v>0</v>
+      </c>
+      <c r="M975" t="n">
+        <v>0</v>
+      </c>
+      <c r="N975" t="n">
+        <v>0</v>
+      </c>
+      <c r="O975" t="n">
+        <v>0</v>
+      </c>
+      <c r="P975" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q975" t="n">
+        <v>0</v>
+      </c>
+      <c r="R975" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z975"/>
+  <dimension ref="A1:Z987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55527,14 +55527,14 @@
     <row r="946" ht="15" customHeight="1">
       <c r="A946" t="inlineStr">
         <is>
-          <t>A 2557-2024</t>
+          <t>A 2528-2024</t>
         </is>
       </c>
       <c r="B946" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55547,7 +55547,7 @@
         </is>
       </c>
       <c r="G946" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -55584,14 +55584,14 @@
     <row r="947" ht="15" customHeight="1">
       <c r="A947" t="inlineStr">
         <is>
-          <t>A 2528-2024</t>
+          <t>A 2557-2024</t>
         </is>
       </c>
       <c r="B947" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         </is>
       </c>
       <c r="G947" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -55641,14 +55641,14 @@
     <row r="948" ht="15" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>A 2965-2024</t>
+          <t>A 2947-2024</t>
         </is>
       </c>
       <c r="B948" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -55698,14 +55698,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 2947-2024</t>
+          <t>A 2964-2024</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55755,14 +55755,14 @@
     <row r="950" ht="15" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>A 2964-2024</t>
+          <t>A 2965-2024</t>
         </is>
       </c>
       <c r="B950" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56040,14 +56040,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 4722-2024</t>
+          <t>A 4733-2024</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -56097,14 +56097,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 4738-2024</t>
+          <t>A 4722-2024</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -56154,14 +56154,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 4733-2024</t>
+          <t>A 4738-2024</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -56218,7 +56218,7 @@
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45336</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56679,7 +56679,7 @@
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56736,7 +56736,7 @@
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>45337</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>45337</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56900,14 +56900,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 6365-2024</t>
+          <t>A 6370-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56957,14 +56957,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 6386-2024</t>
+          <t>A 6367-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -57014,14 +57014,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 6367-2024</t>
+          <t>A 6360-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57034,7 +57034,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57078,7 +57078,7 @@
         <v>45338</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57128,14 +57128,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 6360-2024</t>
+          <t>A 6386-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57148,7 +57148,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -57182,17 +57182,17 @@
       </c>
       <c r="R974" s="2" t="inlineStr"/>
     </row>
-    <row r="975">
+    <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 6370-2024</t>
+          <t>A 6365-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57205,39 +57205,723 @@
         </is>
       </c>
       <c r="G975" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H975" t="n">
+        <v>0</v>
+      </c>
+      <c r="I975" t="n">
+        <v>0</v>
+      </c>
+      <c r="J975" t="n">
+        <v>0</v>
+      </c>
+      <c r="K975" t="n">
+        <v>0</v>
+      </c>
+      <c r="L975" t="n">
+        <v>0</v>
+      </c>
+      <c r="M975" t="n">
+        <v>0</v>
+      </c>
+      <c r="N975" t="n">
+        <v>0</v>
+      </c>
+      <c r="O975" t="n">
+        <v>0</v>
+      </c>
+      <c r="P975" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q975" t="n">
+        <v>0</v>
+      </c>
+      <c r="R975" s="2" t="inlineStr"/>
+    </row>
+    <row r="976" ht="15" customHeight="1">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>A 6672-2024</t>
+        </is>
+      </c>
+      <c r="B976" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C976" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G976" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H976" t="n">
+        <v>0</v>
+      </c>
+      <c r="I976" t="n">
+        <v>0</v>
+      </c>
+      <c r="J976" t="n">
+        <v>0</v>
+      </c>
+      <c r="K976" t="n">
+        <v>0</v>
+      </c>
+      <c r="L976" t="n">
+        <v>0</v>
+      </c>
+      <c r="M976" t="n">
+        <v>0</v>
+      </c>
+      <c r="N976" t="n">
+        <v>0</v>
+      </c>
+      <c r="O976" t="n">
+        <v>0</v>
+      </c>
+      <c r="P976" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q976" t="n">
+        <v>0</v>
+      </c>
+      <c r="R976" s="2" t="inlineStr"/>
+    </row>
+    <row r="977" ht="15" customHeight="1">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>A 6674-2024</t>
+        </is>
+      </c>
+      <c r="B977" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C977" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G977" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H977" t="n">
+        <v>0</v>
+      </c>
+      <c r="I977" t="n">
+        <v>0</v>
+      </c>
+      <c r="J977" t="n">
+        <v>0</v>
+      </c>
+      <c r="K977" t="n">
+        <v>0</v>
+      </c>
+      <c r="L977" t="n">
+        <v>0</v>
+      </c>
+      <c r="M977" t="n">
+        <v>0</v>
+      </c>
+      <c r="N977" t="n">
+        <v>0</v>
+      </c>
+      <c r="O977" t="n">
+        <v>0</v>
+      </c>
+      <c r="P977" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q977" t="n">
+        <v>0</v>
+      </c>
+      <c r="R977" s="2" t="inlineStr"/>
+    </row>
+    <row r="978" ht="15" customHeight="1">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>A 6804-2024</t>
+        </is>
+      </c>
+      <c r="B978" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C978" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G978" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H978" t="n">
+        <v>0</v>
+      </c>
+      <c r="I978" t="n">
+        <v>0</v>
+      </c>
+      <c r="J978" t="n">
+        <v>0</v>
+      </c>
+      <c r="K978" t="n">
+        <v>0</v>
+      </c>
+      <c r="L978" t="n">
+        <v>0</v>
+      </c>
+      <c r="M978" t="n">
+        <v>0</v>
+      </c>
+      <c r="N978" t="n">
+        <v>0</v>
+      </c>
+      <c r="O978" t="n">
+        <v>0</v>
+      </c>
+      <c r="P978" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q978" t="n">
+        <v>0</v>
+      </c>
+      <c r="R978" s="2" t="inlineStr"/>
+    </row>
+    <row r="979" ht="15" customHeight="1">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>A 6808-2024</t>
+        </is>
+      </c>
+      <c r="B979" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C979" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G979" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H979" t="n">
+        <v>0</v>
+      </c>
+      <c r="I979" t="n">
+        <v>0</v>
+      </c>
+      <c r="J979" t="n">
+        <v>0</v>
+      </c>
+      <c r="K979" t="n">
+        <v>0</v>
+      </c>
+      <c r="L979" t="n">
+        <v>0</v>
+      </c>
+      <c r="M979" t="n">
+        <v>0</v>
+      </c>
+      <c r="N979" t="n">
+        <v>0</v>
+      </c>
+      <c r="O979" t="n">
+        <v>0</v>
+      </c>
+      <c r="P979" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q979" t="n">
+        <v>0</v>
+      </c>
+      <c r="R979" s="2" t="inlineStr"/>
+    </row>
+    <row r="980" ht="15" customHeight="1">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>A 6812-2024</t>
+        </is>
+      </c>
+      <c r="B980" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C980" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G980" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H980" t="n">
+        <v>0</v>
+      </c>
+      <c r="I980" t="n">
+        <v>0</v>
+      </c>
+      <c r="J980" t="n">
+        <v>0</v>
+      </c>
+      <c r="K980" t="n">
+        <v>0</v>
+      </c>
+      <c r="L980" t="n">
+        <v>0</v>
+      </c>
+      <c r="M980" t="n">
+        <v>0</v>
+      </c>
+      <c r="N980" t="n">
+        <v>0</v>
+      </c>
+      <c r="O980" t="n">
+        <v>0</v>
+      </c>
+      <c r="P980" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q980" t="n">
+        <v>0</v>
+      </c>
+      <c r="R980" s="2" t="inlineStr"/>
+    </row>
+    <row r="981" ht="15" customHeight="1">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>A 6822-2024</t>
+        </is>
+      </c>
+      <c r="B981" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C981" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G981" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H981" t="n">
+        <v>0</v>
+      </c>
+      <c r="I981" t="n">
+        <v>0</v>
+      </c>
+      <c r="J981" t="n">
+        <v>0</v>
+      </c>
+      <c r="K981" t="n">
+        <v>0</v>
+      </c>
+      <c r="L981" t="n">
+        <v>0</v>
+      </c>
+      <c r="M981" t="n">
+        <v>0</v>
+      </c>
+      <c r="N981" t="n">
+        <v>0</v>
+      </c>
+      <c r="O981" t="n">
+        <v>0</v>
+      </c>
+      <c r="P981" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q981" t="n">
+        <v>0</v>
+      </c>
+      <c r="R981" s="2" t="inlineStr"/>
+    </row>
+    <row r="982" ht="15" customHeight="1">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>A 6826-2024</t>
+        </is>
+      </c>
+      <c r="B982" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C982" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G982" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H982" t="n">
+        <v>0</v>
+      </c>
+      <c r="I982" t="n">
+        <v>0</v>
+      </c>
+      <c r="J982" t="n">
+        <v>0</v>
+      </c>
+      <c r="K982" t="n">
+        <v>0</v>
+      </c>
+      <c r="L982" t="n">
+        <v>0</v>
+      </c>
+      <c r="M982" t="n">
+        <v>0</v>
+      </c>
+      <c r="N982" t="n">
+        <v>0</v>
+      </c>
+      <c r="O982" t="n">
+        <v>0</v>
+      </c>
+      <c r="P982" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q982" t="n">
+        <v>0</v>
+      </c>
+      <c r="R982" s="2" t="inlineStr"/>
+    </row>
+    <row r="983" ht="15" customHeight="1">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>A 6830-2024</t>
+        </is>
+      </c>
+      <c r="B983" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C983" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G983" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H983" t="n">
+        <v>0</v>
+      </c>
+      <c r="I983" t="n">
+        <v>0</v>
+      </c>
+      <c r="J983" t="n">
+        <v>0</v>
+      </c>
+      <c r="K983" t="n">
+        <v>0</v>
+      </c>
+      <c r="L983" t="n">
+        <v>0</v>
+      </c>
+      <c r="M983" t="n">
+        <v>0</v>
+      </c>
+      <c r="N983" t="n">
+        <v>0</v>
+      </c>
+      <c r="O983" t="n">
+        <v>0</v>
+      </c>
+      <c r="P983" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q983" t="n">
+        <v>0</v>
+      </c>
+      <c r="R983" s="2" t="inlineStr"/>
+    </row>
+    <row r="984" ht="15" customHeight="1">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>A 6838-2024</t>
+        </is>
+      </c>
+      <c r="B984" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C984" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G984" t="n">
         <v>0.5</v>
       </c>
-      <c r="H975" t="n">
-        <v>0</v>
-      </c>
-      <c r="I975" t="n">
-        <v>0</v>
-      </c>
-      <c r="J975" t="n">
-        <v>0</v>
-      </c>
-      <c r="K975" t="n">
-        <v>0</v>
-      </c>
-      <c r="L975" t="n">
-        <v>0</v>
-      </c>
-      <c r="M975" t="n">
-        <v>0</v>
-      </c>
-      <c r="N975" t="n">
-        <v>0</v>
-      </c>
-      <c r="O975" t="n">
-        <v>0</v>
-      </c>
-      <c r="P975" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q975" t="n">
-        <v>0</v>
-      </c>
-      <c r="R975" s="2" t="inlineStr"/>
+      <c r="H984" t="n">
+        <v>0</v>
+      </c>
+      <c r="I984" t="n">
+        <v>0</v>
+      </c>
+      <c r="J984" t="n">
+        <v>0</v>
+      </c>
+      <c r="K984" t="n">
+        <v>0</v>
+      </c>
+      <c r="L984" t="n">
+        <v>0</v>
+      </c>
+      <c r="M984" t="n">
+        <v>0</v>
+      </c>
+      <c r="N984" t="n">
+        <v>0</v>
+      </c>
+      <c r="O984" t="n">
+        <v>0</v>
+      </c>
+      <c r="P984" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q984" t="n">
+        <v>0</v>
+      </c>
+      <c r="R984" s="2" t="inlineStr"/>
+    </row>
+    <row r="985" ht="15" customHeight="1">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>A 6835-2024</t>
+        </is>
+      </c>
+      <c r="B985" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C985" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G985" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H985" t="n">
+        <v>0</v>
+      </c>
+      <c r="I985" t="n">
+        <v>0</v>
+      </c>
+      <c r="J985" t="n">
+        <v>0</v>
+      </c>
+      <c r="K985" t="n">
+        <v>0</v>
+      </c>
+      <c r="L985" t="n">
+        <v>0</v>
+      </c>
+      <c r="M985" t="n">
+        <v>0</v>
+      </c>
+      <c r="N985" t="n">
+        <v>0</v>
+      </c>
+      <c r="O985" t="n">
+        <v>0</v>
+      </c>
+      <c r="P985" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q985" t="n">
+        <v>0</v>
+      </c>
+      <c r="R985" s="2" t="inlineStr"/>
+    </row>
+    <row r="986" ht="15" customHeight="1">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>A 6815-2024</t>
+        </is>
+      </c>
+      <c r="B986" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C986" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G986" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H986" t="n">
+        <v>0</v>
+      </c>
+      <c r="I986" t="n">
+        <v>0</v>
+      </c>
+      <c r="J986" t="n">
+        <v>0</v>
+      </c>
+      <c r="K986" t="n">
+        <v>0</v>
+      </c>
+      <c r="L986" t="n">
+        <v>0</v>
+      </c>
+      <c r="M986" t="n">
+        <v>0</v>
+      </c>
+      <c r="N986" t="n">
+        <v>0</v>
+      </c>
+      <c r="O986" t="n">
+        <v>0</v>
+      </c>
+      <c r="P986" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q986" t="n">
+        <v>0</v>
+      </c>
+      <c r="R986" s="2" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>A 6840-2024</t>
+        </is>
+      </c>
+      <c r="B987" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C987" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G987" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H987" t="n">
+        <v>0</v>
+      </c>
+      <c r="I987" t="n">
+        <v>0</v>
+      </c>
+      <c r="J987" t="n">
+        <v>0</v>
+      </c>
+      <c r="K987" t="n">
+        <v>0</v>
+      </c>
+      <c r="L987" t="n">
+        <v>0</v>
+      </c>
+      <c r="M987" t="n">
+        <v>0</v>
+      </c>
+      <c r="N987" t="n">
+        <v>0</v>
+      </c>
+      <c r="O987" t="n">
+        <v>0</v>
+      </c>
+      <c r="P987" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q987" t="n">
+        <v>0</v>
+      </c>
+      <c r="R987" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z987"/>
+  <dimension ref="A1:Z988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55641,14 +55641,14 @@
     <row r="948" ht="15" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>A 2947-2024</t>
+          <t>A 2965-2024</t>
         </is>
       </c>
       <c r="B948" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -55698,14 +55698,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 2964-2024</t>
+          <t>A 2947-2024</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55755,14 +55755,14 @@
     <row r="950" ht="15" customHeight="1">
       <c r="A950" t="inlineStr">
         <is>
-          <t>A 2965-2024</t>
+          <t>A 2964-2024</t>
         </is>
       </c>
       <c r="B950" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56211,14 +56211,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 4766-2024</t>
+          <t>A 4767-2024</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56268,14 +56268,14 @@
     <row r="959" ht="15" customHeight="1">
       <c r="A959" t="inlineStr">
         <is>
-          <t>A 4767-2024</t>
+          <t>A 4756-2024</t>
         </is>
       </c>
       <c r="B959" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="H959" t="n">
         <v>0</v>
@@ -56325,14 +56325,14 @@
     <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 4756-2024</t>
+          <t>A 4766-2024</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -56389,7 +56389,7 @@
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56615,14 +56615,14 @@
     <row r="965" ht="15" customHeight="1">
       <c r="A965" t="inlineStr">
         <is>
-          <t>A 5982-2024</t>
+          <t>A 5809-2024</t>
         </is>
       </c>
       <c r="B965" s="1" t="n">
-        <v>45336</v>
+        <v>45335</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56634,8 +56634,13 @@
           <t>ALVESTA</t>
         </is>
       </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G965" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -56679,7 +56684,7 @@
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56729,14 +56734,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 6020-2024</t>
+          <t>A 5982-2024</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56749,7 +56754,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56786,14 +56791,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 6100-2024</t>
+          <t>A 6020-2024</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
-        <v>45337</v>
+        <v>45336</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56806,7 +56811,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56843,14 +56848,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 6094-2024</t>
+          <t>A 6100-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56863,7 +56868,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56900,14 +56905,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 6370-2024</t>
+          <t>A 6094-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
-        <v>45338</v>
+        <v>45337</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56920,7 +56925,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56957,14 +56962,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 6367-2024</t>
+          <t>A 6370-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57014,14 +57019,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 6360-2024</t>
+          <t>A 6365-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57034,7 +57039,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57071,14 +57076,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 6368-2024</t>
+          <t>A 6360-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57091,7 +57096,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57128,14 +57133,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 6386-2024</t>
+          <t>A 6368-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57148,7 +57153,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -57185,14 +57190,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 6365-2024</t>
+          <t>A 6386-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57205,7 +57210,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57242,14 +57247,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 6672-2024</t>
+          <t>A 6367-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
-        <v>45341</v>
+        <v>45338</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57262,7 +57267,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -57299,14 +57304,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 6674-2024</t>
+          <t>A 6672-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57319,7 +57324,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57356,14 +57361,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 6804-2024</t>
+          <t>A 6674-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
-        <v>45342</v>
+        <v>45341</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57376,7 +57381,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -57413,14 +57418,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 6808-2024</t>
+          <t>A 6815-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57433,7 +57438,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -57470,14 +57475,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 6812-2024</t>
+          <t>A 6840-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57490,7 +57495,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57527,14 +57532,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 6822-2024</t>
+          <t>A 6835-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57547,7 +57552,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57584,14 +57589,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 6826-2024</t>
+          <t>A 6804-2024</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57604,7 +57609,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -57641,14 +57646,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 6830-2024</t>
+          <t>A 6808-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57661,7 +57666,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -57698,14 +57703,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 6838-2024</t>
+          <t>A 6812-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57718,7 +57723,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -57755,14 +57760,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 6835-2024</t>
+          <t>A 6822-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57775,7 +57780,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -57812,14 +57817,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6815-2024</t>
+          <t>A 6826-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57832,7 +57837,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57866,17 +57871,17 @@
       </c>
       <c r="R986" s="2" t="inlineStr"/>
     </row>
-    <row r="987">
+    <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 6840-2024</t>
+          <t>A 6830-2024</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57889,7 +57894,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57922,6 +57927,63 @@
         <v>0</v>
       </c>
       <c r="R987" s="2" t="inlineStr"/>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>A 6838-2024</t>
+        </is>
+      </c>
+      <c r="B988" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C988" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G988" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H988" t="n">
+        <v>0</v>
+      </c>
+      <c r="I988" t="n">
+        <v>0</v>
+      </c>
+      <c r="J988" t="n">
+        <v>0</v>
+      </c>
+      <c r="K988" t="n">
+        <v>0</v>
+      </c>
+      <c r="L988" t="n">
+        <v>0</v>
+      </c>
+      <c r="M988" t="n">
+        <v>0</v>
+      </c>
+      <c r="N988" t="n">
+        <v>0</v>
+      </c>
+      <c r="O988" t="n">
+        <v>0</v>
+      </c>
+      <c r="P988" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q988" t="n">
+        <v>0</v>
+      </c>
+      <c r="R988" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56211,14 +56211,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 4767-2024</t>
+          <t>A 4766-2024</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56268,14 +56268,14 @@
     <row r="959" ht="15" customHeight="1">
       <c r="A959" t="inlineStr">
         <is>
-          <t>A 4756-2024</t>
+          <t>A 4767-2024</t>
         </is>
       </c>
       <c r="B959" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="H959" t="n">
         <v>0</v>
@@ -56325,14 +56325,14 @@
     <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 4766-2024</t>
+          <t>A 4756-2024</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -56389,7 +56389,7 @@
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45335</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56677,14 +56677,14 @@
     <row r="966" ht="15" customHeight="1">
       <c r="A966" t="inlineStr">
         <is>
-          <t>A 6009-2024</t>
+          <t>A 5982-2024</t>
         </is>
       </c>
       <c r="B966" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56697,7 +56697,7 @@
         </is>
       </c>
       <c r="G966" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -56734,14 +56734,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 5982-2024</t>
+          <t>A 6009-2024</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56798,7 +56798,7 @@
         <v>45336</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56848,14 +56848,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 6100-2024</t>
+          <t>A 6094-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56905,14 +56905,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 6094-2024</t>
+          <t>A 6100-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56962,14 +56962,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 6370-2024</t>
+          <t>A 6360-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -57026,7 +57026,7 @@
         <v>45338</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57076,14 +57076,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 6360-2024</t>
+          <t>A 6370-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57096,7 +57096,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57140,7 +57140,7 @@
         <v>45338</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45338</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45338</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57311,7 +57311,7 @@
         <v>45341</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>45341</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57418,14 +57418,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 6815-2024</t>
+          <t>A 6808-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -57475,14 +57475,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 6840-2024</t>
+          <t>A 6804-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57532,14 +57532,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 6835-2024</t>
+          <t>A 6812-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57589,14 +57589,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 6804-2024</t>
+          <t>A 6822-2024</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -57646,14 +57646,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 6808-2024</t>
+          <t>A 6826-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -57703,14 +57703,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 6812-2024</t>
+          <t>A 6830-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -57760,14 +57760,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 6822-2024</t>
+          <t>A 6838-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -57817,14 +57817,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6826-2024</t>
+          <t>A 6815-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57837,7 +57837,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57874,14 +57874,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 6830-2024</t>
+          <t>A 6840-2024</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57931,14 +57931,14 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>A 6838-2024</t>
+          <t>A 6835-2024</t>
         </is>
       </c>
       <c r="B988" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57951,7 +57951,7 @@
         </is>
       </c>
       <c r="G988" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z988"/>
+  <dimension ref="A1:Z991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55641,14 +55641,14 @@
     <row r="948" ht="15" customHeight="1">
       <c r="A948" t="inlineStr">
         <is>
-          <t>A 2965-2024</t>
+          <t>A 2947-2024</t>
         </is>
       </c>
       <c r="B948" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         </is>
       </c>
       <c r="G948" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -55698,14 +55698,14 @@
     <row r="949" ht="15" customHeight="1">
       <c r="A949" t="inlineStr">
         <is>
-          <t>A 2947-2024</t>
+          <t>A 2965-2024</t>
         </is>
       </c>
       <c r="B949" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         </is>
       </c>
       <c r="G949" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -55762,7 +55762,7 @@
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56040,14 +56040,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 4733-2024</t>
+          <t>A 4767-2024</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -56097,14 +56097,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 4722-2024</t>
+          <t>A 4756-2024</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -56154,14 +56154,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 4738-2024</t>
+          <t>A 4722-2024</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -56211,14 +56211,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 4766-2024</t>
+          <t>A 4738-2024</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56268,14 +56268,14 @@
     <row r="959" ht="15" customHeight="1">
       <c r="A959" t="inlineStr">
         <is>
-          <t>A 4767-2024</t>
+          <t>A 4766-2024</t>
         </is>
       </c>
       <c r="B959" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H959" t="n">
         <v>0</v>
@@ -56325,14 +56325,14 @@
     <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 4756-2024</t>
+          <t>A 4733-2024</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -56389,7 +56389,7 @@
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45335</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56734,14 +56734,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 6009-2024</t>
+          <t>A 6020-2024</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56791,14 +56791,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 6020-2024</t>
+          <t>A 6009-2024</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56811,7 +56811,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56848,14 +56848,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 6094-2024</t>
+          <t>A 6100-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56905,14 +56905,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 6100-2024</t>
+          <t>A 6094-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56962,14 +56962,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 6360-2024</t>
+          <t>A 6365-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -57019,14 +57019,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 6365-2024</t>
+          <t>A 6386-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57076,14 +57076,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 6370-2024</t>
+          <t>A 6360-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57096,7 +57096,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57140,7 +57140,7 @@
         <v>45338</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57190,14 +57190,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 6386-2024</t>
+          <t>A 6367-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57247,14 +57247,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 6367-2024</t>
+          <t>A 6370-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57304,14 +57304,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 6672-2024</t>
+          <t>A 6674-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57324,7 +57324,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57361,14 +57361,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 6674-2024</t>
+          <t>A 6672-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -57425,7 +57425,7 @@
         <v>45342</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57475,14 +57475,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 6804-2024</t>
+          <t>A 6815-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57539,7 +57539,7 @@
         <v>45342</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         <v>45342</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57653,7 +57653,7 @@
         <v>45342</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57710,7 +57710,7 @@
         <v>45342</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57767,7 +57767,7 @@
         <v>45342</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57817,14 +57817,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6815-2024</t>
+          <t>A 6840-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57837,7 +57837,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57874,14 +57874,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 6840-2024</t>
+          <t>A 6804-2024</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57928,7 +57928,7 @@
       </c>
       <c r="R987" s="2" t="inlineStr"/>
     </row>
-    <row r="988">
+    <row r="988" ht="15" customHeight="1">
       <c r="A988" t="inlineStr">
         <is>
           <t>A 6835-2024</t>
@@ -57938,7 +57938,7 @@
         <v>45342</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57984,6 +57984,182 @@
         <v>0</v>
       </c>
       <c r="R988" s="2" t="inlineStr"/>
+    </row>
+    <row r="989" ht="15" customHeight="1">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>A 6919-2024</t>
+        </is>
+      </c>
+      <c r="B989" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C989" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G989" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H989" t="n">
+        <v>0</v>
+      </c>
+      <c r="I989" t="n">
+        <v>0</v>
+      </c>
+      <c r="J989" t="n">
+        <v>0</v>
+      </c>
+      <c r="K989" t="n">
+        <v>0</v>
+      </c>
+      <c r="L989" t="n">
+        <v>0</v>
+      </c>
+      <c r="M989" t="n">
+        <v>0</v>
+      </c>
+      <c r="N989" t="n">
+        <v>0</v>
+      </c>
+      <c r="O989" t="n">
+        <v>0</v>
+      </c>
+      <c r="P989" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q989" t="n">
+        <v>0</v>
+      </c>
+      <c r="R989" s="2" t="inlineStr"/>
+    </row>
+    <row r="990" ht="15" customHeight="1">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>A 7342-2024</t>
+        </is>
+      </c>
+      <c r="B990" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C990" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G990" t="n">
+        <v>2</v>
+      </c>
+      <c r="H990" t="n">
+        <v>0</v>
+      </c>
+      <c r="I990" t="n">
+        <v>0</v>
+      </c>
+      <c r="J990" t="n">
+        <v>0</v>
+      </c>
+      <c r="K990" t="n">
+        <v>0</v>
+      </c>
+      <c r="L990" t="n">
+        <v>0</v>
+      </c>
+      <c r="M990" t="n">
+        <v>0</v>
+      </c>
+      <c r="N990" t="n">
+        <v>0</v>
+      </c>
+      <c r="O990" t="n">
+        <v>0</v>
+      </c>
+      <c r="P990" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q990" t="n">
+        <v>0</v>
+      </c>
+      <c r="R990" s="2" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>A 7338-2024</t>
+        </is>
+      </c>
+      <c r="B991" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C991" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G991" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H991" t="n">
+        <v>0</v>
+      </c>
+      <c r="I991" t="n">
+        <v>0</v>
+      </c>
+      <c r="J991" t="n">
+        <v>0</v>
+      </c>
+      <c r="K991" t="n">
+        <v>0</v>
+      </c>
+      <c r="L991" t="n">
+        <v>0</v>
+      </c>
+      <c r="M991" t="n">
+        <v>0</v>
+      </c>
+      <c r="N991" t="n">
+        <v>0</v>
+      </c>
+      <c r="O991" t="n">
+        <v>0</v>
+      </c>
+      <c r="P991" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q991" t="n">
+        <v>0</v>
+      </c>
+      <c r="R991" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55812,14 +55812,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 3506-2024</t>
+          <t>A 3510-2024</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55869,14 +55869,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 3510-2024</t>
+          <t>A 3506-2024</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56040,14 +56040,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 4767-2024</t>
+          <t>A 4756-2024</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -56097,14 +56097,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 4756-2024</t>
+          <t>A 4767-2024</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -56161,7 +56161,7 @@
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56382,14 +56382,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 4871-2024</t>
+          <t>A 5045-2024</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56439,14 +56439,14 @@
     <row r="962" ht="15" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>A 5045-2024</t>
+          <t>A 4871-2024</t>
         </is>
       </c>
       <c r="B962" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45335</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45336</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45337</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45337</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45338</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57019,14 +57019,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 6386-2024</t>
+          <t>A 6367-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57076,14 +57076,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 6360-2024</t>
+          <t>A 6386-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57096,7 +57096,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57133,14 +57133,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 6368-2024</t>
+          <t>A 6370-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -57190,14 +57190,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 6367-2024</t>
+          <t>A 6368-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57247,14 +57247,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 6370-2024</t>
+          <t>A 6360-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -57304,14 +57304,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 6674-2024</t>
+          <t>A 6672-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57324,7 +57324,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57361,14 +57361,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 6672-2024</t>
+          <t>A 6674-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -57418,14 +57418,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 6808-2024</t>
+          <t>A 6812-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -57475,14 +57475,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 6815-2024</t>
+          <t>A 6808-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57532,14 +57532,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 6812-2024</t>
+          <t>A 6804-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57589,14 +57589,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 6822-2024</t>
+          <t>A 6835-2024</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -57646,14 +57646,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 6826-2024</t>
+          <t>A 6840-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -57703,14 +57703,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 6830-2024</t>
+          <t>A 6815-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -57767,7 +57767,7 @@
         <v>45342</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57817,14 +57817,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6840-2024</t>
+          <t>A 6830-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57837,7 +57837,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57874,14 +57874,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 6804-2024</t>
+          <t>A 6826-2024</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57931,14 +57931,14 @@
     <row r="988" ht="15" customHeight="1">
       <c r="A988" t="inlineStr">
         <is>
-          <t>A 6835-2024</t>
+          <t>A 6822-2024</t>
         </is>
       </c>
       <c r="B988" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57951,7 +57951,7 @@
         </is>
       </c>
       <c r="G988" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>
@@ -57995,7 +57995,7 @@
         <v>45343</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45345</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45345</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56040,14 +56040,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 4756-2024</t>
+          <t>A 4722-2024</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -56097,14 +56097,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 4767-2024</t>
+          <t>A 4738-2024</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -56154,14 +56154,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 4722-2024</t>
+          <t>A 4766-2024</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -56211,14 +56211,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 4738-2024</t>
+          <t>A 4756-2024</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56268,14 +56268,14 @@
     <row r="959" ht="15" customHeight="1">
       <c r="A959" t="inlineStr">
         <is>
-          <t>A 4766-2024</t>
+          <t>A 4767-2024</t>
         </is>
       </c>
       <c r="B959" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         </is>
       </c>
       <c r="G959" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H959" t="n">
         <v>0</v>
@@ -56332,7 +56332,7 @@
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45335</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56741,7 +56741,7 @@
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>45336</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56855,7 +56855,7 @@
         <v>45337</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>45337</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56962,14 +56962,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 6365-2024</t>
+          <t>A 6360-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -57019,14 +57019,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 6367-2024</t>
+          <t>A 6368-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57076,14 +57076,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 6386-2024</t>
+          <t>A 6365-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57096,7 +57096,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57133,14 +57133,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 6370-2024</t>
+          <t>A 6386-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -57190,14 +57190,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 6368-2024</t>
+          <t>A 6367-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57247,14 +57247,14 @@
     <row r="976" ht="15" customHeight="1">
       <c r="A976" t="inlineStr">
         <is>
-          <t>A 6360-2024</t>
+          <t>A 6370-2024</t>
         </is>
       </c>
       <c r="B976" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         </is>
       </c>
       <c r="G976" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -57304,14 +57304,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 6672-2024</t>
+          <t>A 6674-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57324,7 +57324,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57361,14 +57361,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 6674-2024</t>
+          <t>A 6672-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -57418,14 +57418,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 6812-2024</t>
+          <t>A 6815-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57475,14 +57475,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 6808-2024</t>
+          <t>A 6840-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57539,7 +57539,7 @@
         <v>45342</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         <v>45342</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57646,14 +57646,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 6840-2024</t>
+          <t>A 6808-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -57703,14 +57703,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 6815-2024</t>
+          <t>A 6812-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57767,7 +57767,7 @@
         <v>45342</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45342</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57938,7 +57938,7 @@
         <v>45342</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57995,7 +57995,7 @@
         <v>45343</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45345</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45345</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z991"/>
+  <dimension ref="A1:Z992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55812,14 +55812,14 @@
     <row r="951" ht="15" customHeight="1">
       <c r="A951" t="inlineStr">
         <is>
-          <t>A 3510-2024</t>
+          <t>A 3506-2024</t>
         </is>
       </c>
       <c r="B951" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         </is>
       </c>
       <c r="G951" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -55869,14 +55869,14 @@
     <row r="952" ht="15" customHeight="1">
       <c r="A952" t="inlineStr">
         <is>
-          <t>A 3506-2024</t>
+          <t>A 3510-2024</t>
         </is>
       </c>
       <c r="B952" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         </is>
       </c>
       <c r="G952" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56040,14 +56040,14 @@
     <row r="955" ht="15" customHeight="1">
       <c r="A955" t="inlineStr">
         <is>
-          <t>A 4722-2024</t>
+          <t>A 4733-2024</t>
         </is>
       </c>
       <c r="B955" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         </is>
       </c>
       <c r="G955" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="H955" t="n">
         <v>0</v>
@@ -56097,14 +56097,14 @@
     <row r="956" ht="15" customHeight="1">
       <c r="A956" t="inlineStr">
         <is>
-          <t>A 4738-2024</t>
+          <t>A 4722-2024</t>
         </is>
       </c>
       <c r="B956" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         </is>
       </c>
       <c r="G956" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -56154,14 +56154,14 @@
     <row r="957" ht="15" customHeight="1">
       <c r="A957" t="inlineStr">
         <is>
-          <t>A 4766-2024</t>
+          <t>A 4738-2024</t>
         </is>
       </c>
       <c r="B957" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         </is>
       </c>
       <c r="G957" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="H957" t="n">
         <v>0</v>
@@ -56211,14 +56211,14 @@
     <row r="958" ht="15" customHeight="1">
       <c r="A958" t="inlineStr">
         <is>
-          <t>A 4756-2024</t>
+          <t>A 4766-2024</t>
         </is>
       </c>
       <c r="B958" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         </is>
       </c>
       <c r="G958" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -56275,7 +56275,7 @@
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56325,14 +56325,14 @@
     <row r="960" ht="15" customHeight="1">
       <c r="A960" t="inlineStr">
         <is>
-          <t>A 4733-2024</t>
+          <t>A 4756-2024</t>
         </is>
       </c>
       <c r="B960" s="1" t="n">
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         </is>
       </c>
       <c r="G960" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -56382,14 +56382,14 @@
     <row r="961" ht="15" customHeight="1">
       <c r="A961" t="inlineStr">
         <is>
-          <t>A 5045-2024</t>
+          <t>A 4871-2024</t>
         </is>
       </c>
       <c r="B961" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         </is>
       </c>
       <c r="G961" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H961" t="n">
         <v>0</v>
@@ -56439,14 +56439,14 @@
     <row r="962" ht="15" customHeight="1">
       <c r="A962" t="inlineStr">
         <is>
-          <t>A 4871-2024</t>
+          <t>A 5045-2024</t>
         </is>
       </c>
       <c r="B962" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         </is>
       </c>
       <c r="G962" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -56503,7 +56503,7 @@
         <v>45330</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>45331</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45335</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45336</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56734,14 +56734,14 @@
     <row r="967" ht="15" customHeight="1">
       <c r="A967" t="inlineStr">
         <is>
-          <t>A 6020-2024</t>
+          <t>A 6009-2024</t>
         </is>
       </c>
       <c r="B967" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         </is>
       </c>
       <c r="G967" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -56791,14 +56791,14 @@
     <row r="968" ht="15" customHeight="1">
       <c r="A968" t="inlineStr">
         <is>
-          <t>A 6009-2024</t>
+          <t>A 6020-2024</t>
         </is>
       </c>
       <c r="B968" s="1" t="n">
         <v>45336</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56811,7 +56811,7 @@
         </is>
       </c>
       <c r="G968" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -56848,14 +56848,14 @@
     <row r="969" ht="15" customHeight="1">
       <c r="A969" t="inlineStr">
         <is>
-          <t>A 6100-2024</t>
+          <t>A 6094-2024</t>
         </is>
       </c>
       <c r="B969" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         </is>
       </c>
       <c r="G969" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="H969" t="n">
         <v>0</v>
@@ -56905,14 +56905,14 @@
     <row r="970" ht="15" customHeight="1">
       <c r="A970" t="inlineStr">
         <is>
-          <t>A 6094-2024</t>
+          <t>A 6100-2024</t>
         </is>
       </c>
       <c r="B970" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         </is>
       </c>
       <c r="G970" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -56962,14 +56962,14 @@
     <row r="971" ht="15" customHeight="1">
       <c r="A971" t="inlineStr">
         <is>
-          <t>A 6360-2024</t>
+          <t>A 6365-2024</t>
         </is>
       </c>
       <c r="B971" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         </is>
       </c>
       <c r="G971" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H971" t="n">
         <v>0</v>
@@ -57019,14 +57019,14 @@
     <row r="972" ht="15" customHeight="1">
       <c r="A972" t="inlineStr">
         <is>
-          <t>A 6368-2024</t>
+          <t>A 6386-2024</t>
         </is>
       </c>
       <c r="B972" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         </is>
       </c>
       <c r="G972" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -57076,14 +57076,14 @@
     <row r="973" ht="15" customHeight="1">
       <c r="A973" t="inlineStr">
         <is>
-          <t>A 6365-2024</t>
+          <t>A 6367-2024</t>
         </is>
       </c>
       <c r="B973" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57096,7 +57096,7 @@
         </is>
       </c>
       <c r="G973" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -57133,14 +57133,14 @@
     <row r="974" ht="15" customHeight="1">
       <c r="A974" t="inlineStr">
         <is>
-          <t>A 6386-2024</t>
+          <t>A 6360-2024</t>
         </is>
       </c>
       <c r="B974" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         </is>
       </c>
       <c r="G974" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H974" t="n">
         <v>0</v>
@@ -57190,14 +57190,14 @@
     <row r="975" ht="15" customHeight="1">
       <c r="A975" t="inlineStr">
         <is>
-          <t>A 6367-2024</t>
+          <t>A 6368-2024</t>
         </is>
       </c>
       <c r="B975" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         </is>
       </c>
       <c r="G975" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -57254,7 +57254,7 @@
         <v>45338</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57304,14 +57304,14 @@
     <row r="977" ht="15" customHeight="1">
       <c r="A977" t="inlineStr">
         <is>
-          <t>A 6674-2024</t>
+          <t>A 6672-2024</t>
         </is>
       </c>
       <c r="B977" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57324,7 +57324,7 @@
         </is>
       </c>
       <c r="G977" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -57361,14 +57361,14 @@
     <row r="978" ht="15" customHeight="1">
       <c r="A978" t="inlineStr">
         <is>
-          <t>A 6672-2024</t>
+          <t>A 6674-2024</t>
         </is>
       </c>
       <c r="B978" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         </is>
       </c>
       <c r="G978" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H978" t="n">
         <v>0</v>
@@ -57418,14 +57418,14 @@
     <row r="979" ht="15" customHeight="1">
       <c r="A979" t="inlineStr">
         <is>
-          <t>A 6815-2024</t>
+          <t>A 6804-2024</t>
         </is>
       </c>
       <c r="B979" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         </is>
       </c>
       <c r="G979" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H979" t="n">
         <v>0</v>
@@ -57475,14 +57475,14 @@
     <row r="980" ht="15" customHeight="1">
       <c r="A980" t="inlineStr">
         <is>
-          <t>A 6840-2024</t>
+          <t>A 6835-2024</t>
         </is>
       </c>
       <c r="B980" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         </is>
       </c>
       <c r="G980" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H980" t="n">
         <v>0</v>
@@ -57532,14 +57532,14 @@
     <row r="981" ht="15" customHeight="1">
       <c r="A981" t="inlineStr">
         <is>
-          <t>A 6804-2024</t>
+          <t>A 6808-2024</t>
         </is>
       </c>
       <c r="B981" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         </is>
       </c>
       <c r="G981" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="H981" t="n">
         <v>0</v>
@@ -57589,14 +57589,14 @@
     <row r="982" ht="15" customHeight="1">
       <c r="A982" t="inlineStr">
         <is>
-          <t>A 6835-2024</t>
+          <t>A 6812-2024</t>
         </is>
       </c>
       <c r="B982" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         </is>
       </c>
       <c r="G982" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H982" t="n">
         <v>0</v>
@@ -57646,14 +57646,14 @@
     <row r="983" ht="15" customHeight="1">
       <c r="A983" t="inlineStr">
         <is>
-          <t>A 6808-2024</t>
+          <t>A 6822-2024</t>
         </is>
       </c>
       <c r="B983" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         </is>
       </c>
       <c r="G983" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="H983" t="n">
         <v>0</v>
@@ -57703,14 +57703,14 @@
     <row r="984" ht="15" customHeight="1">
       <c r="A984" t="inlineStr">
         <is>
-          <t>A 6812-2024</t>
+          <t>A 6826-2024</t>
         </is>
       </c>
       <c r="B984" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57723,7 +57723,7 @@
         </is>
       </c>
       <c r="G984" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="H984" t="n">
         <v>0</v>
@@ -57760,14 +57760,14 @@
     <row r="985" ht="15" customHeight="1">
       <c r="A985" t="inlineStr">
         <is>
-          <t>A 6838-2024</t>
+          <t>A 6830-2024</t>
         </is>
       </c>
       <c r="B985" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         </is>
       </c>
       <c r="G985" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="H985" t="n">
         <v>0</v>
@@ -57817,14 +57817,14 @@
     <row r="986" ht="15" customHeight="1">
       <c r="A986" t="inlineStr">
         <is>
-          <t>A 6830-2024</t>
+          <t>A 6838-2024</t>
         </is>
       </c>
       <c r="B986" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57837,7 +57837,7 @@
         </is>
       </c>
       <c r="G986" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -57874,14 +57874,14 @@
     <row r="987" ht="15" customHeight="1">
       <c r="A987" t="inlineStr">
         <is>
-          <t>A 6826-2024</t>
+          <t>A 6815-2024</t>
         </is>
       </c>
       <c r="B987" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         </is>
       </c>
       <c r="G987" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="H987" t="n">
         <v>0</v>
@@ -57931,14 +57931,14 @@
     <row r="988" ht="15" customHeight="1">
       <c r="A988" t="inlineStr">
         <is>
-          <t>A 6822-2024</t>
+          <t>A 6840-2024</t>
         </is>
       </c>
       <c r="B988" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -57951,7 +57951,7 @@
         </is>
       </c>
       <c r="G988" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="H988" t="n">
         <v>0</v>
@@ -57995,7 +57995,7 @@
         <v>45343</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45345</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
       </c>
       <c r="R990" s="2" t="inlineStr"/>
     </row>
-    <row r="991">
+    <row r="991" ht="15" customHeight="1">
       <c r="A991" t="inlineStr">
         <is>
           <t>A 7338-2024</t>
@@ -58114,7 +58114,7 @@
         <v>45345</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58160,6 +58160,63 @@
         <v>0</v>
       </c>
       <c r="R991" s="2" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>A 7586-2024</t>
+        </is>
+      </c>
+      <c r="B992" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C992" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>KRONOBERGS LÄN</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>ALVESTA</t>
+        </is>
+      </c>
+      <c r="G992" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H992" t="n">
+        <v>0</v>
+      </c>
+      <c r="I992" t="n">
+        <v>0</v>
+      </c>
+      <c r="J992" t="n">
+        <v>0</v>
+      </c>
+      <c r="K992" t="n">
+        <v>0</v>
+      </c>
+      <c r="L992" t="n">
+        <v>0</v>
+      </c>
+      <c r="M992" t="n">
+        <v>0</v>
+      </c>
+      <c r="N992" t="n">
+        <v>0</v>
+      </c>
+      <c r="O992" t="n">
+        <v>0</v>
+      </c>
+      <c r="P992" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q992" t="n">
+        <v>0</v>
+      </c>
+      <c r="R992" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALVESTA.xlsx
+++ b/Översikt ALVESTA.xlsx
@@ -569,7 +569,7 @@
         <v>45146</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>45239</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>44085</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>45328</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44319</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>43486</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>43560</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>43728</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44535</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>44592</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45245</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>43355</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>43475</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>43497</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>43523</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>43560</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>43591</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>43612</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>43741</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>44130</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44459</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44810</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>44819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45043</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>45106</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>45160</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45166</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45187</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45188</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45310</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>43318</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>43322</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>43326</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>43329</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>43332</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>43335</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>43339</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>43343</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>43347</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>43350</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>43350</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>43356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>43367</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>43369</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>43382</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>43390</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>43395</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43399</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43399</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>43402</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>43403</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>43403</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>43403</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>43408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>43408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>43409</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>43411</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>43416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>43416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>43418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>43419</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>43420</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>43423</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>43427</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>43430</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>43431</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>43433</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>43434</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>43439</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>43440</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>43440</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>43440</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>43441</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>43441</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>43444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>43447</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>43447</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>43448</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>43451</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>43452</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43462</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>43467</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>43467</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>43468</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>43473</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>43473</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>43475</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>43475</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>43479</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>43480</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>43481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>43486</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>43488</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>43488</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>43489</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>43493</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>43493</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>43493</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>43493</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>43494</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>43496</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>43497</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>43500</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>43502</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>43503</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>43504</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>43507</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>43507</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>43510</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>43510</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>43522</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>43523</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>43523</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>43523</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>43523</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>43529</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>43534</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>43534</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>43537</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>43537</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>43537</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>43537</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>43537</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>43537</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>43538</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>43545</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>43552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>43552</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>43560</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>43560</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>43560</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>43563</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>43572</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>43580</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>43587</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>43593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>43601</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>43605</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>43605</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>43606</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43607</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43608</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43608</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43608</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>43609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>43609</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>43612</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>43612</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>43616</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>43621</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43626</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43627</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>43628</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>43630</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>43633</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>43634</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>43634</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>43636</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>43636</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>43636</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>43636</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>43644</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>43651</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43653</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>43654</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>43655</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>43655</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>43661</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>43664</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>43664</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>43664</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>43667</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>43667</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>43667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>43668</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>43668</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>43669</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>43672</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>43675</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43683</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43684</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43690</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43690</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43690</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43690</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43698</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>43704</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>43706</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>43706</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>43707</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>43711</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>43711</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>43712</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>43714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>43717</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>43718</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>43725</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>43728</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43728</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>43728</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>43728</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>43728</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>43732</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>43733</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>43734</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>43735</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>43739</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>43739</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>43740</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>43747</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>43747</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>43747</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>43747</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>43747</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>43747</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>43747</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>43747</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>43747</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>43747</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43747</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43747</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43747</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43747</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43747</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43747</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43747</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43747</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43747</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43747</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43747</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43749</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43749</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43753</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43753</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43753</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43755</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43756</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>43759</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>43774</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>43774</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>43774</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>43774</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>43774</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>43777</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>43777</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>43781</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>43787</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>43794</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>43795</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>43795</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>43795</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>43795</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>43798</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>43801</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>43802</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>43808</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>43816</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>43817</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>43817</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>43817</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>43819</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>43819</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>43826</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>43826</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>43826</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>43835</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>43837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>43838</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>43839</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>43840</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>43843</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>43853</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>43853</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>43853</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>43854</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>43854</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>43858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>43858</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>43858</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>43859</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>43868</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>43871</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>43878</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>43879</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>43879</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>43880</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>43886</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>43893</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>43893</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>43893</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>43893</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>43894</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>43895</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>43901</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>43915</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>43915</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>43921</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>43941</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>43941</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>43955</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>43962</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>43970</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>43979</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>43979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>43985</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>43992</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43992</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44000</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44000</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44000</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44000</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44000</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44004</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44004</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44007</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44012</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44012</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44012</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44014</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44014</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44016</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44016</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>44016</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44018</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>44018</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>44018</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44018</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44022</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44022</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44032</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44035</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>44036</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44046</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44047</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44048</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44048</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44049</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44050</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44051</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44053</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44054</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>44054</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44056</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44056</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44060</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>44061</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44061</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44062</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44064</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44064</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44067</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44076</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44077</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>44078</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44078</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44078</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44078</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>44084</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>44085</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>44089</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>44095</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44109</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>44111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44113</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44115</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44115</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44116</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44117</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44123</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44124</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44124</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44125</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44137</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44141</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44141</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>44144</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44147</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>44151</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44151</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44153</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>44159</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44159</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44165</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44165</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44165</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44172</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44174</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44174</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44175</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44175</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44175</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>44182</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>44186</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44186</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>44188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>44200</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44200</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44207</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44210</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44211</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44216</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44216</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44232</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44236</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>44236</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>44238</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44239</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>44243</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>44243</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>44249</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>44252</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44256</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44256</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>44257</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44257</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44264</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>44271</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44292</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44293</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44295</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>44295</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>44305</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44306</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44306</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44306</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>44307</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>44309</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>44309</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44313</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44313</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44320</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>44323</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44323</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>44326</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>44328</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44335</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>44336</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44336</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>44340</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>44351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44351</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44354</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>44362</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44363</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>44364</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>44365</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44369</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44382</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44385</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44385</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>44386</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44390</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44399</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>44401</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44404</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44412</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44412</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44418</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44419</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44419</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44424</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44431</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44434</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44434</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44434</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44434</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44434</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44434</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44435</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44438</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44438</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44441</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44442</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44442</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44442</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44442</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44442</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>44445</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44445</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>44446</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44447</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>44448</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>44454</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44454</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44454</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>44454</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>44455</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>44455</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44455</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44461</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44461</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>44461</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44462</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>44467</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44469</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44477</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44477</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44480</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44487</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44487</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>44488</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44490</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44490</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44495</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>44495</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>44496</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>44497</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44502</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>44504</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44504</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>44511</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44511</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44512</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44512</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44515</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44515</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44517</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>44518</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>44523</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44523</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>44526</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44530</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>44538</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>44545</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44565</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44569</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>44573</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>44581</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>44586</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>44592</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>44597</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44597</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44597</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>44600</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>44601</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44601</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>44601</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44606</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44606</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44606</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44606</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44608</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44609</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44609</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44613</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44613</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44613</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44613</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44615</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>44615</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>44615</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44615</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44615</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44620</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>44620</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44635</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44635</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44635</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>44642</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>44648</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>44649</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44657</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44659</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44663</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>44670</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44687</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44692</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44693</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44693</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44693</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44706</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44706</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44728</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44734</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>44734</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>44735</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44735</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44735</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44735</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44735</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>44739</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>44739</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44740</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44741</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44743</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44743</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>44743</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44743</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44747</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>44749</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44749</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>44754</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44768</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44768</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>44782</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>44783</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>44783</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44783</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44788</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>44798</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44798</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>44800</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44804</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>44805</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>44805</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37653,7 +37653,7 @@
         <v>44805</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>44805</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44809</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44810</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44812</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44816</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>44816</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>44823</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>44823</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>44823</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44824</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44827</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44833</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>44838</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44839</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44841</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>44853</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44854</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44854</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>44854</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>44855</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44859</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>44859</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44859</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44867</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>44868</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>44868</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>44879</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44881</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>44882</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44893</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44894</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>44895</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>44900</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44900</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44901</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>44901</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>44901</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>44907</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>44909</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44909</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>44911</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>44914</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>44925</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44925</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>44935</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>44935</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>44935</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>44935</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44935</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44935</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>44938</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>44938</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44943</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44948</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>44950</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>44957</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>44958</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>44966</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44970</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>44970</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44972</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44973</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44974</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44974</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44978</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44979</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44985</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>44988</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>44988</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>44991</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>44991</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>44991</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44994</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44994</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>44995</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>44998</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44998</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44998</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44998</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45005</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45005</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45009</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45012</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45012</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45014</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45015</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45015</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45015</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45032</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45032</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45033</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45040</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45040</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45041</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45043</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45043</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45045</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45049</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45049</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45054</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45054</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45055</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45055</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45055</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45061</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>45062</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45063</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45068</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45068</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45075</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45075</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45076</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45076</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45076</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>45076</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45078</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45079</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45079</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45082</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45086</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45086</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>45089</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45092</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45092</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45095</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45099</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>45099</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45101</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45101</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45103</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45103</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45103</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45103</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>45105</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45105</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45106</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45106</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45106</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45106</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45110</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45110</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45110</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45110</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45110</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45110</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45112</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45113</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45113</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45113</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45113</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45113</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45113</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45114</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45114</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>45114</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45127</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45128</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45128</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45128</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45128</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45135</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45135</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45136</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45136</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47928,7 +47928,7 @@
         <v>45146</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45146</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45149</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>45152</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45153</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45153</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45153</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>45153</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45153</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48726,7 +48726,7 @@
         <v>45155</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>45155</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45155</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45155</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45155</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45155</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>45159</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45161</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45161</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45162</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45163</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45163</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45166</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45166</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45166</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45166</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45166</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45166</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45169</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45171</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45180</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45180</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45182</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45187</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45187</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45187</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45188</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45189</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45189</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45196</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45196</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45196</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45198</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45198</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45198</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45198</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45202</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45202</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45202</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45210</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45210</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>45210</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45216</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45216</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45216</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45217</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45217</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45217</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45217</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45217</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45217</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45217</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45217</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45217</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45218</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45219</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45229</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45230</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>45230</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45230</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52508,7 +52508,7 @@
         <v>45230</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45230</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>45231</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45231</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>45231</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45236</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52907,7 +52907,7 @@
         <v>45236</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>45239</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45245</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45246</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45247</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45247</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45247</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45247</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45251</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>45251</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45251</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45257</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45259</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53705,7 +53705,7 @@
         <v>45259</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45259</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45261</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45264</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45264</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53990,7 +53990,7 @@
         <v>45265</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>45266</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45267</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45267</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54218,7 +54218,7 @@
         <v>45267</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>45268</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>45272</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45272</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45281</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45282</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45288</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45288</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45288</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45289</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45300</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45300</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45302</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>45302</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45302</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45305</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45307</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45307</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>45308</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45308</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45308</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45308</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45313</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45315</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45315</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>45315</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45320</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45320</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45322</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45324</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45328</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>45328</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>45328</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45328</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>45328</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>45329</v>
       </c>
       <c r=